--- a/artfynd/A 49148-2021 artfynd.xlsx
+++ b/artfynd/A 49148-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 49148-2021 artfynd.xlsx
+++ b/artfynd/A 49148-2021 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>82522366</v>
       </c>
       <c r="B2" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100761</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>610096.4124869888</v>
+        <v>610096</v>
       </c>
       <c r="R2" t="n">
-        <v>6826145.809026469</v>
+        <v>6826146</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -753,19 +748,9 @@
           <t>1988-07-02</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1988-07-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -804,12 +789,7 @@
         <v>82522423</v>
       </c>
       <c r="B3" t="n">
-        <v>96336</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98581</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -841,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>610095.1534930776</v>
+        <v>610095</v>
       </c>
       <c r="R3" t="n">
-        <v>6826245.455058883</v>
+        <v>6826245</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -879,19 +859,9 @@
           <t>1988-07-02</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1988-07-02</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -930,12 +900,7 @@
         <v>82522373</v>
       </c>
       <c r="B4" t="n">
-        <v>96367</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98613</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -967,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>610096.4124869888</v>
+        <v>610096</v>
       </c>
       <c r="R4" t="n">
-        <v>6826145.809026469</v>
+        <v>6826146</v>
       </c>
       <c r="S4" t="n">
         <v>100</v>
@@ -1005,19 +970,9 @@
           <t>1988-07-02</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1988-07-02</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1056,12 +1011,7 @@
         <v>82522394</v>
       </c>
       <c r="B5" t="n">
-        <v>103250</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105606</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1093,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>610095.1534930776</v>
+        <v>610095</v>
       </c>
       <c r="R5" t="n">
-        <v>6826245.455058883</v>
+        <v>6826245</v>
       </c>
       <c r="S5" t="n">
         <v>100</v>
@@ -1131,19 +1081,9 @@
           <t>1988-07-02</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>1988-07-02</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1182,12 +1122,7 @@
         <v>82522349</v>
       </c>
       <c r="B6" t="n">
-        <v>103250</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105606</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1219,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>610096.4124869888</v>
+        <v>610096</v>
       </c>
       <c r="R6" t="n">
-        <v>6826145.809026469</v>
+        <v>6826146</v>
       </c>
       <c r="S6" t="n">
         <v>100</v>
@@ -1257,19 +1192,9 @@
           <t>1988-07-02</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>1988-07-02</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1308,12 +1233,7 @@
         <v>82522365</v>
       </c>
       <c r="B7" t="n">
-        <v>98980</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101225</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1345,10 +1265,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>610096.4124869888</v>
+        <v>610096</v>
       </c>
       <c r="R7" t="n">
-        <v>6826145.809026469</v>
+        <v>6826146</v>
       </c>
       <c r="S7" t="n">
         <v>100</v>
@@ -1383,19 +1303,9 @@
           <t>1988-07-02</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>1988-07-02</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1434,12 +1344,7 @@
         <v>82522383</v>
       </c>
       <c r="B8" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97454</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1471,10 +1376,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>610096.4124869888</v>
+        <v>610096</v>
       </c>
       <c r="R8" t="n">
-        <v>6826145.809026469</v>
+        <v>6826146</v>
       </c>
       <c r="S8" t="n">
         <v>100</v>
@@ -1509,19 +1414,9 @@
           <t>1988-07-02</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>1988-07-02</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1560,12 +1455,7 @@
         <v>82522419</v>
       </c>
       <c r="B9" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100761</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1597,10 +1487,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>610095.1534930776</v>
+        <v>610095</v>
       </c>
       <c r="R9" t="n">
-        <v>6826245.455058883</v>
+        <v>6826245</v>
       </c>
       <c r="S9" t="n">
         <v>100</v>
@@ -1635,19 +1525,9 @@
           <t>1988-07-02</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>1988-07-02</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1686,12 +1566,7 @@
         <v>82522352</v>
       </c>
       <c r="B10" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104028</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1723,10 +1598,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>610096.4124869888</v>
+        <v>610096</v>
       </c>
       <c r="R10" t="n">
-        <v>6826145.809026469</v>
+        <v>6826146</v>
       </c>
       <c r="S10" t="n">
         <v>100</v>
@@ -1761,19 +1636,9 @@
           <t>1988-07-02</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>1988-07-02</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 49148-2021 artfynd.xlsx
+++ b/artfynd/A 49148-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>82522366</v>
       </c>
       <c r="B2" t="n">
-        <v>100761</v>
+        <v>100768</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>82522423</v>
       </c>
       <c r="B3" t="n">
-        <v>98581</v>
+        <v>98587</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>82522373</v>
       </c>
       <c r="B4" t="n">
-        <v>98613</v>
+        <v>98619</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>82522394</v>
       </c>
       <c r="B5" t="n">
-        <v>105606</v>
+        <v>105615</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>82522349</v>
       </c>
       <c r="B6" t="n">
-        <v>105606</v>
+        <v>105615</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>82522365</v>
       </c>
       <c r="B7" t="n">
-        <v>101225</v>
+        <v>101232</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>82522383</v>
       </c>
       <c r="B8" t="n">
-        <v>97454</v>
+        <v>97460</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>82522419</v>
       </c>
       <c r="B9" t="n">
-        <v>100761</v>
+        <v>100768</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>82522352</v>
       </c>
       <c r="B10" t="n">
-        <v>104028</v>
+        <v>104036</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 49148-2021 artfynd.xlsx
+++ b/artfynd/A 49148-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>82522366</v>
       </c>
       <c r="B2" t="n">
-        <v>100768</v>
+        <v>100773</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>82522423</v>
       </c>
       <c r="B3" t="n">
-        <v>98587</v>
+        <v>98590</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>82522373</v>
       </c>
       <c r="B4" t="n">
-        <v>98619</v>
+        <v>98622</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>82522394</v>
       </c>
       <c r="B5" t="n">
-        <v>105615</v>
+        <v>105627</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>82522349</v>
       </c>
       <c r="B6" t="n">
-        <v>105615</v>
+        <v>105627</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>82522365</v>
       </c>
       <c r="B7" t="n">
-        <v>101232</v>
+        <v>101237</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>82522383</v>
       </c>
       <c r="B8" t="n">
-        <v>97460</v>
+        <v>97462</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>82522419</v>
       </c>
       <c r="B9" t="n">
-        <v>100768</v>
+        <v>100773</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>82522352</v>
       </c>
       <c r="B10" t="n">
-        <v>104036</v>
+        <v>104048</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 49148-2021 artfynd.xlsx
+++ b/artfynd/A 49148-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>82522366</v>
       </c>
       <c r="B2" t="n">
-        <v>100773</v>
+        <v>100779</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>82522423</v>
       </c>
       <c r="B3" t="n">
-        <v>98590</v>
+        <v>98593</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>82522373</v>
       </c>
       <c r="B4" t="n">
-        <v>98622</v>
+        <v>98625</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>82522394</v>
       </c>
       <c r="B5" t="n">
-        <v>105627</v>
+        <v>105636</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>82522349</v>
       </c>
       <c r="B6" t="n">
-        <v>105627</v>
+        <v>105636</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>82522365</v>
       </c>
       <c r="B7" t="n">
-        <v>101237</v>
+        <v>101243</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>82522419</v>
       </c>
       <c r="B9" t="n">
-        <v>100773</v>
+        <v>100779</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>82522352</v>
       </c>
       <c r="B10" t="n">
-        <v>104048</v>
+        <v>104057</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 49148-2021 artfynd.xlsx
+++ b/artfynd/A 49148-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>82522366</v>
       </c>
       <c r="B2" t="n">
-        <v>100779</v>
+        <v>100780</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>82522423</v>
       </c>
       <c r="B3" t="n">
-        <v>98593</v>
+        <v>98594</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>82522373</v>
       </c>
       <c r="B4" t="n">
-        <v>98625</v>
+        <v>98626</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>82522394</v>
       </c>
       <c r="B5" t="n">
-        <v>105636</v>
+        <v>105639</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>82522349</v>
       </c>
       <c r="B6" t="n">
-        <v>105636</v>
+        <v>105639</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>82522365</v>
       </c>
       <c r="B7" t="n">
-        <v>101243</v>
+        <v>101244</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>82522383</v>
       </c>
       <c r="B8" t="n">
-        <v>97462</v>
+        <v>97463</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>82522419</v>
       </c>
       <c r="B9" t="n">
-        <v>100779</v>
+        <v>100780</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>82522352</v>
       </c>
       <c r="B10" t="n">
-        <v>104057</v>
+        <v>104060</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 49148-2021 artfynd.xlsx
+++ b/artfynd/A 49148-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>82522366</v>
       </c>
       <c r="B2" t="n">
-        <v>100780</v>
+        <v>100807</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>82522423</v>
       </c>
       <c r="B3" t="n">
-        <v>98594</v>
+        <v>98621</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>82522373</v>
       </c>
       <c r="B4" t="n">
-        <v>98626</v>
+        <v>98653</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>82522394</v>
       </c>
       <c r="B5" t="n">
-        <v>105639</v>
+        <v>105667</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>82522349</v>
       </c>
       <c r="B6" t="n">
-        <v>105639</v>
+        <v>105667</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>82522365</v>
       </c>
       <c r="B7" t="n">
-        <v>101244</v>
+        <v>101271</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>82522383</v>
       </c>
       <c r="B8" t="n">
-        <v>97463</v>
+        <v>97490</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>82522419</v>
       </c>
       <c r="B9" t="n">
-        <v>100780</v>
+        <v>100807</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>82522352</v>
       </c>
       <c r="B10" t="n">
-        <v>104060</v>
+        <v>104087</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 49148-2021 artfynd.xlsx
+++ b/artfynd/A 49148-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>82522366</v>
       </c>
       <c r="B2" t="n">
-        <v>100807</v>
+        <v>100813</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>82522423</v>
       </c>
       <c r="B3" t="n">
-        <v>98621</v>
+        <v>98627</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>82522373</v>
       </c>
       <c r="B4" t="n">
-        <v>98653</v>
+        <v>98659</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>82522394</v>
       </c>
       <c r="B5" t="n">
-        <v>105667</v>
+        <v>105673</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>82522349</v>
       </c>
       <c r="B6" t="n">
-        <v>105667</v>
+        <v>105673</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>82522365</v>
       </c>
       <c r="B7" t="n">
-        <v>101271</v>
+        <v>101277</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>82522383</v>
       </c>
       <c r="B8" t="n">
-        <v>97490</v>
+        <v>97496</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>82522419</v>
       </c>
       <c r="B9" t="n">
-        <v>100807</v>
+        <v>100813</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>82522352</v>
       </c>
       <c r="B10" t="n">
-        <v>104087</v>
+        <v>104093</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 49148-2021 artfynd.xlsx
+++ b/artfynd/A 49148-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>82522366</v>
       </c>
       <c r="B2" t="n">
-        <v>100813</v>
+        <v>100820</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>82522423</v>
       </c>
       <c r="B3" t="n">
-        <v>98627</v>
+        <v>98634</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>82522373</v>
       </c>
       <c r="B4" t="n">
-        <v>98659</v>
+        <v>98666</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>82522394</v>
       </c>
       <c r="B5" t="n">
-        <v>105673</v>
+        <v>105680</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>82522349</v>
       </c>
       <c r="B6" t="n">
-        <v>105673</v>
+        <v>105680</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>82522365</v>
       </c>
       <c r="B7" t="n">
-        <v>101277</v>
+        <v>101284</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>82522383</v>
       </c>
       <c r="B8" t="n">
-        <v>97496</v>
+        <v>97503</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>82522419</v>
       </c>
       <c r="B9" t="n">
-        <v>100813</v>
+        <v>100820</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>82522352</v>
       </c>
       <c r="B10" t="n">
-        <v>104093</v>
+        <v>104100</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 49148-2021 artfynd.xlsx
+++ b/artfynd/A 49148-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>82522366</v>
       </c>
       <c r="B2" t="n">
-        <v>100820</v>
+        <v>100824</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>82522423</v>
       </c>
       <c r="B3" t="n">
-        <v>98634</v>
+        <v>98638</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>82522373</v>
       </c>
       <c r="B4" t="n">
-        <v>98666</v>
+        <v>98670</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>82522394</v>
       </c>
       <c r="B5" t="n">
-        <v>105680</v>
+        <v>105684</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>82522349</v>
       </c>
       <c r="B6" t="n">
-        <v>105680</v>
+        <v>105684</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>82522365</v>
       </c>
       <c r="B7" t="n">
-        <v>101284</v>
+        <v>101288</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>82522383</v>
       </c>
       <c r="B8" t="n">
-        <v>97503</v>
+        <v>97507</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>82522419</v>
       </c>
       <c r="B9" t="n">
-        <v>100820</v>
+        <v>100824</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>82522352</v>
       </c>
       <c r="B10" t="n">
-        <v>104100</v>
+        <v>104104</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 49148-2021 artfynd.xlsx
+++ b/artfynd/A 49148-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>82522366</v>
       </c>
       <c r="B2" t="n">
-        <v>100824</v>
+        <v>100831</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>82522423</v>
       </c>
       <c r="B3" t="n">
-        <v>98638</v>
+        <v>98645</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>82522373</v>
       </c>
       <c r="B4" t="n">
-        <v>98670</v>
+        <v>98677</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>82522394</v>
       </c>
       <c r="B5" t="n">
-        <v>105684</v>
+        <v>105691</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>82522349</v>
       </c>
       <c r="B6" t="n">
-        <v>105684</v>
+        <v>105691</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>82522365</v>
       </c>
       <c r="B7" t="n">
-        <v>101288</v>
+        <v>101295</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>82522383</v>
       </c>
       <c r="B8" t="n">
-        <v>97507</v>
+        <v>97514</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>82522419</v>
       </c>
       <c r="B9" t="n">
-        <v>100824</v>
+        <v>100831</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>82522352</v>
       </c>
       <c r="B10" t="n">
-        <v>104104</v>
+        <v>104111</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 49148-2021 artfynd.xlsx
+++ b/artfynd/A 49148-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>82522366</v>
       </c>
       <c r="B2" t="n">
-        <v>100834</v>
+        <v>100839</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>82522423</v>
       </c>
       <c r="B3" t="n">
-        <v>98648</v>
+        <v>98653</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>82522373</v>
       </c>
       <c r="B4" t="n">
-        <v>98680</v>
+        <v>98685</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>82522394</v>
       </c>
       <c r="B5" t="n">
-        <v>105694</v>
+        <v>105699</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>82522349</v>
       </c>
       <c r="B6" t="n">
-        <v>105694</v>
+        <v>105699</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>82522365</v>
       </c>
       <c r="B7" t="n">
-        <v>101298</v>
+        <v>101303</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>82522383</v>
       </c>
       <c r="B8" t="n">
-        <v>97517</v>
+        <v>97522</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>82522419</v>
       </c>
       <c r="B9" t="n">
-        <v>100834</v>
+        <v>100839</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>82522352</v>
       </c>
       <c r="B10" t="n">
-        <v>104114</v>
+        <v>104119</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 49148-2021 artfynd.xlsx
+++ b/artfynd/A 49148-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>82522366</v>
       </c>
       <c r="B2" t="n">
-        <v>100839</v>
+        <v>100847</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>82522423</v>
       </c>
       <c r="B3" t="n">
-        <v>98653</v>
+        <v>98661</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>82522373</v>
       </c>
       <c r="B4" t="n">
-        <v>98685</v>
+        <v>98693</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>82522394</v>
       </c>
       <c r="B5" t="n">
-        <v>105699</v>
+        <v>105707</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>82522349</v>
       </c>
       <c r="B6" t="n">
-        <v>105699</v>
+        <v>105707</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>82522365</v>
       </c>
       <c r="B7" t="n">
-        <v>101303</v>
+        <v>101311</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>82522383</v>
       </c>
       <c r="B8" t="n">
-        <v>97522</v>
+        <v>97530</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>82522419</v>
       </c>
       <c r="B9" t="n">
-        <v>100839</v>
+        <v>100847</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>82522352</v>
       </c>
       <c r="B10" t="n">
-        <v>104119</v>
+        <v>104127</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 49148-2021 artfynd.xlsx
+++ b/artfynd/A 49148-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>82522366</v>
+        <v>82522423</v>
       </c>
       <c r="B2" t="n">
-        <v>100847</v>
+        <v>99120</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>219811</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Borka, Hls</t>
+          <t>Sandarna, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>610096</v>
+        <v>610095</v>
       </c>
       <c r="R2" t="n">
-        <v>6826146</v>
+        <v>6826245</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -740,7 +740,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>MAX198807021400</t>
+          <t>MAX198807021230</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Fuktig granskog</t>
+          <t>Fuktig skogsäng</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>82522423</v>
+        <v>82522373</v>
       </c>
       <c r="B3" t="n">
-        <v>98661</v>
+        <v>99153</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,34 +797,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219811</v>
+        <v>219874</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sandarna, Hls</t>
+          <t>Borka, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>610095</v>
+        <v>610096</v>
       </c>
       <c r="R3" t="n">
-        <v>6826245</v>
+        <v>6826146</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -851,7 +851,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>MAX198807021230</t>
+          <t>MAX198807021400</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -875,7 +875,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Fuktig skogsäng</t>
+          <t>Fuktig granskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>82522373</v>
+        <v>82522349</v>
       </c>
       <c r="B4" t="n">
-        <v>98693</v>
+        <v>106229</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219874</v>
+        <v>221725</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -1011,7 +1011,7 @@
         <v>82522394</v>
       </c>
       <c r="B5" t="n">
-        <v>105707</v>
+        <v>106229</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>82522349</v>
+        <v>82522383</v>
       </c>
       <c r="B6" t="n">
-        <v>105707</v>
+        <v>97983</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1130,21 +1130,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221725</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1230,27 +1230,27 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>82522365</v>
+        <v>82522352</v>
       </c>
       <c r="B7" t="n">
-        <v>101311</v>
+        <v>104628</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222929</v>
+        <v>222412</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Backruta</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Thalictrum simplex</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1341,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>82522383</v>
+        <v>82522366</v>
       </c>
       <c r="B8" t="n">
-        <v>97530</v>
+        <v>101326</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1352,21 +1352,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1455,7 +1455,7 @@
         <v>82522419</v>
       </c>
       <c r="B9" t="n">
-        <v>100847</v>
+        <v>101326</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1563,27 +1563,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>82522352</v>
+        <v>82522365</v>
       </c>
       <c r="B10" t="n">
-        <v>104127</v>
+        <v>101794</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222412</v>
+        <v>222929</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Backruta</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Thalictrum simplex</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
